--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 09 D100 Spring 2024 24GH00I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 09 D100 Spring 2024 24GH00I33 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44355BBA-AB0A-409C-B1BD-CB3AB664A8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F742336D-F707-41A3-9B88-00BBD82FE695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{311B88C8-13AE-4F19-BAB2-2AA4B18D0462}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{311B88C8-13AE-4F19-BAB2-2AA4B18D0462}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId2"/>
+    <pivotCache cacheId="27" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4077,7 +4077,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC18902-AB38-458D-9665-CB97C0A39B4C}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC18902-AB38-458D-9665-CB97C0A39B4C}" name="PivotTable1" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4523,18 +4523,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19CF9FD-CB9B-4D66-BC19-E46B939E347F}">
   <dimension ref="A1:Y192"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4587,7 +4588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4646,7 +4647,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4785,7 +4786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4853,7 +4854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -4921,7 +4922,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -4989,7 +4990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5122,7 +5123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -5187,7 +5188,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5317,7 +5318,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -5388,7 +5389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -5527,7 +5528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -5595,7 +5596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5719,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -5781,7 +5782,7 @@
         <v>1.004</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -5841,7 +5842,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -5903,7 +5904,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -5963,7 +5964,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -6023,7 +6024,7 @@
       </c>
       <c r="V23" s="6"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -6083,7 +6084,7 @@
       </c>
       <c r="V24" s="6"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -6140,7 +6141,7 @@
       </c>
       <c r="U25" s="6"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -6193,7 +6194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -6246,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -6352,7 +6353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -6405,7 +6406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -6511,7 +6512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -6564,7 +6565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -6617,7 +6618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -6670,7 +6671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -6723,7 +6724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -6829,7 +6830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -6882,7 +6883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -6935,7 +6936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -6988,7 +6989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -7041,7 +7042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -7094,7 +7095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -7147,7 +7148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -7253,7 +7254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -7359,7 +7360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -7412,7 +7413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -7465,7 +7466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -7518,7 +7519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -7571,7 +7572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -7624,7 +7625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -7730,7 +7731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -7783,7 +7784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -7836,7 +7837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -7995,7 +7996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -8048,7 +8049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -8101,7 +8102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -8154,7 +8155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -8207,7 +8208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -8260,7 +8261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -8313,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -8366,7 +8367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -8419,7 +8420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -8472,7 +8473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -8525,7 +8526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -8631,7 +8632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -8684,7 +8685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -8737,7 +8738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -8790,7 +8791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -8843,7 +8844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -8896,7 +8897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -8949,7 +8950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -9002,7 +9003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -9055,7 +9056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -9108,7 +9109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -9161,7 +9162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -9214,7 +9215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -9267,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -9373,7 +9374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -9426,7 +9427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -9479,7 +9480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -9532,7 +9533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -9585,7 +9586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -9638,7 +9639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -9691,7 +9692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -9744,7 +9745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -9797,7 +9798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -9903,7 +9904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -9956,7 +9957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -10009,7 +10010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -10062,7 +10063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -10115,7 +10116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -10168,7 +10169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -10221,7 +10222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -10274,7 +10275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -10327,7 +10328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -10380,7 +10381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -10433,7 +10434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -10539,7 +10540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -10592,7 +10593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -10645,7 +10646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -10698,7 +10699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -10751,7 +10752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -10804,7 +10805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -10857,7 +10858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -10910,7 +10911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -10963,7 +10964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -11016,7 +11017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -11069,7 +11070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -11122,7 +11123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -11175,7 +11176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -11228,7 +11229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>17</v>
       </c>
@@ -11281,7 +11282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -11334,7 +11335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -11387,7 +11388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>17</v>
       </c>
@@ -11440,7 +11441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -11493,7 +11494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -11546,7 +11547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -11599,7 +11600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -11652,7 +11653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -11705,7 +11706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -11758,7 +11759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -11811,7 +11812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -11864,7 +11865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -11917,7 +11918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -11970,7 +11971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -12023,7 +12024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -12076,7 +12077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -12129,7 +12130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -12182,7 +12183,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -12235,7 +12236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -12288,7 +12289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -12341,7 +12342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -12394,7 +12395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -12447,7 +12448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -12500,7 +12501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -12553,7 +12554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -12606,7 +12607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -12659,7 +12660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -12712,7 +12713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -12765,7 +12766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -12818,7 +12819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>17</v>
       </c>
@@ -12871,7 +12872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>17</v>
       </c>
@@ -12924,7 +12925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>17</v>
       </c>
@@ -12977,7 +12978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>17</v>
       </c>
@@ -13030,7 +13031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>17</v>
       </c>
@@ -13083,7 +13084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>17</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>17</v>
       </c>
@@ -13189,7 +13190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>17</v>
       </c>
@@ -13242,7 +13243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -13295,7 +13296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -13348,7 +13349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>17</v>
       </c>
@@ -13401,7 +13402,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>17</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>17</v>
       </c>
@@ -13507,7 +13508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>17</v>
       </c>
@@ -13560,7 +13561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>17</v>
       </c>
@@ -13613,7 +13614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>17</v>
       </c>
@@ -13666,7 +13667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>17</v>
       </c>
@@ -13719,7 +13720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -13772,7 +13773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>17</v>
       </c>
@@ -13825,7 +13826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>17</v>
       </c>
@@ -13878,7 +13879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>17</v>
       </c>
@@ -13931,7 +13932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>17</v>
       </c>
@@ -13984,7 +13985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>17</v>
       </c>
@@ -14037,7 +14038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>17</v>
       </c>
@@ -14143,7 +14144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -14196,7 +14197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>17</v>
       </c>
@@ -14249,7 +14250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>17</v>
       </c>
@@ -14302,7 +14303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>17</v>
       </c>
@@ -14355,7 +14356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>17</v>
       </c>
@@ -14408,7 +14409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>17</v>
       </c>
@@ -14461,7 +14462,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -14514,7 +14515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -14567,7 +14568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -14620,7 +14621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -14673,7 +14674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -14726,7 +14727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>17</v>
       </c>
@@ -14779,7 +14780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>17</v>
       </c>
@@ -14832,7 +14833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>17</v>
       </c>
@@ -14885,7 +14886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>17</v>
       </c>
@@ -14932,13 +14933,13 @@
         <v>39</v>
       </c>
       <c r="P191" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q191" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>17</v>
       </c>
@@ -14985,7 +14986,7 @@
         <v>39</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q192" s="2">
         <v>0</v>
